--- a/output/graficos_nacionales/plot_glosario_e_mat_a_2024_nacional.xlsx
+++ b/output/graficos_nacionales/plot_glosario_e_mat_a_2024_nacional.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 03:56</t>
+    <t xml:space="preserve">2026-10-05 06:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
